--- a/sheets/real-estate/commercial-nnn-lease-analyzer/commercial-nnn-lease-analyzer.xlsx
+++ b/sheets/real-estate/commercial-nnn-lease-analyzer/commercial-nnn-lease-analyzer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\000_drive_drive\600_PROJECTS\modelstack\sheets\real-estate\commercial-nnn-lease-analyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C3E026-CD5F-4775-8C65-C2916C3EA5D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB93FA82-5C83-4E10-AFCD-8CFA0575E840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Property Overview" sheetId="1" r:id="rId1"/>
@@ -510,7 +510,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -576,8 +576,21 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF4472C4"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -598,6 +611,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -622,7 +641,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -652,6 +671,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2074,10 +2095,10 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="B30" s="19">
+      <c r="B30" s="30">
         <f>IF(B6=0,0,B28/B6)</f>
         <v>0.8571428571428571</v>
       </c>
